--- a/05_statistics/pathway_conflict_ai_resolved.xlsx
+++ b/05_statistics/pathway_conflict_ai_resolved.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETOH_005</t>
+          <t>ETOH_009</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -483,75 +483,123 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P1;P5</t>
+          <t>P2;P5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+          <t>{'final_mentioned_pathways': 'P2;P5', 'final_main_pathways': 'P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper proposes a tandem catalyst with dual active sites (Sn and O) that enable C-C coupling between *CHO and *CO(OH) (P2) and between formate/HCOOH and *CO(OH) (P5) to form ethanol. Evidence includes DFT calculations, isotope labeling, and product distribution experiments.', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>P2;P5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Isotope labeling experiments (S0050) directly support P5 (formate/HCOOH coupling with *CO(OH)), while P2 (*CHO + *CO(OH)) is discussed but lacks direct experimental confirmation. DFT evidence for P5 is also strong, and the paper's main conclusion emphasizes the formate-bicarbonate coupling pathway.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>use_resolved_result</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETOH_005</t>
+          <t>ETOH_016</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>same_pathway_main_and_reject</t>
+          <t>multiple_main_pathways</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P1;P3;P6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+          <t>{'final_mentioned_pathways': 'P1;P3;P6', 'final_main_pathways': 'P1;P3;P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>P3;P6</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>P1;P3;P6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>P3 and P6 are directly supported by operando spectroscopy evidence for ethanol. P1 is mainly associated with ethylene, and its ethanol specificity is weaker. The conflict for P6 arises because DFT rejects CO-CH coupling (one mechanism), but SERS confirms the *OCHCH intermediate, so the pathway is retained. P1 is demoted to mentioned pathway due to lack of strong ethanol evidence.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>use_resolved_result</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ETOH_005</t>
+          <t>ETOH_016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>low_confidence_but_included</t>
+          <t>same_pathway_main_and_reject</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1 included rows</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+          <t>{'final_mentioned_pathways': 'P1;P3;P6', 'final_main_pathways': 'P1;P3;P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>P1;P3;P6</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>P1;P3;P5;P6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>P1 (OCCO pathway) is supported by operando spectroscopy for ethylene and ethanol; P3 (*CHCO→*OCHCH2) is directly identified as selectivity switch to ethanol; P6 (*OCHCH) is confirmed as common intermediate by SERS and labeling experiments, despite DFT rejecting CO-CH coupling on defective sites (which is a separate mechanism). The rejection of P6 in sentence S0044 refers specifically to CO-CH coupling, not the *OCHCH pathway supported elsewhere. Therefore, P6 is retained as main pathway.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>use_resolved_result</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETOH_009</t>
+          <t>ETOH_023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -561,512 +609,118 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P1;P3;P4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;isotope;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+          <t>{'final_mentioned_pathways': 'P1;P3;P4', 'final_main_pathways': 'P1;P3;P4', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'This paper focuses on electrocatalytic CO2 reduction to ethanol via subsurface Co-doped CuS catalyst. The main pathways involve asymmetric C-C coupling (*CO + *COH → *OCCOH) and subsequent hydrogenation steps to ethanol (P1, P3, P4), supported by DFT calculations and in-situ FTIR spectroscopy. Key evidence includes explicit ethanol pathway in S0246 and shared intermediate *CHCHO in S0040.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>P1;P3;P4</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>P1;P3;P4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>The paper presents a complete ethanol pathway from CO to ethanol via asymmetric C-C coupling (*CO+*COH→*OCCOH) and subsequent hydrogenation steps including *CHCHO intermediate. Sentence S0246 explicitly lists this pathway, which corresponds to P1, P3, and P4 as a sequential mechanism. Therefore, all three pathways are supported as main pathways in a unified mechanism, consistent with the original paper summary.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>keep_paper_summary</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ETOH_009</t>
+          <t>ETOH_024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>low_confidence_but_included</t>
+          <t>multiple_main_pathways</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1 included rows</t>
+          <t>P1;P2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;isotope;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+          <t>{'final_mentioned_pathways': 'P1;P2', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '通过DFT和原位光谱证实CA分子促进*OC2H3中间体C-O键保留，有利于乙醇生成，主要路径为P1和P2。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P1;P2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>P1;P2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>The paper explicitly identifies P1 and P2 as the main pathways, supported by DFT and operando spectroscopy evidence. Low-confidence sentences that do not mention ethanol pathways are excluded. The conflict is resolved by retaining both pathways as main, consistent with the original paper-level summary.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>use_resolved_result</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ETOH_011</t>
+          <t>ETOH_B2_017</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>same_pathway_main_and_reject</t>
+          <t>multiple_main_pathways</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>P1;P2;P3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'final_mentioned_pathways': 'P1;P2;P3', 'final_main_pathways': 'P1;P2;P3', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper focuses on low-coordinated Cu catalysts for CO2 reduction to C2+ alcohols, primarily ethanol. DFT calculations and operando Raman spectroscopy identify pathways P1 (*OCCOH intermediate via *CO-COH coupling), P2 (*CH2CO intermediate), and P3 (*CO-COH coupling) as main routes. Evidence includes DFT energy barriers and spectroscopic detection of key intermediates (*OCCOH, *CHO, *OCH2CH3). While ethanol is the dominant product (FE ~56%), the paper often refers to C2+ alcohols generally, leading to a partial ethanol-specific level.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1', 'final_main_pathways': 'P1', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'operando/spectroscopy;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ETOH_011</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2 included rows</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1', 'final_main_pathways': 'P1', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'operando/spectroscopy;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ETOH_012</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2 included rows</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P5', 'final_main_pathways': 'P5', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'product inference;review', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ETOH_014</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1', 'final_main_pathways': nan, 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'product inference', 'ai_paper_reason': 'Sentence-level AI review found pathway mentions for P1, but no main-pathway claim.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ETOH_016</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>multiple_main_pathways</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>P1;P3;P5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P3;P5;P6', 'final_main_pathways': 'P1;P3;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;isotope;DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;isotope;operando/spectroscopy;product inference;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P3;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ETOH_016</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4 included rows</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P3;P5;P6', 'final_main_pathways': 'P1;P3;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;isotope;DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;isotope;operando/spectroscopy;product inference;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P3;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ETOH_017</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>multiple_main_pathways</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>P1;P2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ETOH_017</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ETOH_024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>multiple_main_pathways</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>P1;P2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': 'P1;P2;P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ETOH_024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>same_pathway_main_and_reject</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>P1;P2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': 'P1;P2;P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ETOH_024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P5', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': 'P1;P2;P5', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;product inference;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ETOH_B2_005</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P5', 'final_main_pathways': 'P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;product inference;operando/spectroscopy;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ETOH_B2_011</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>multiple_main_pathways</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>P1;P5</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P4;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ETOH_B2_011</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>same_pathway_main_and_reject</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P4;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ETOH_B2_011</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2 included rows</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P4;P5', 'final_main_pathways': 'P1;P5', 'final_rejected_pathways': 'P1', 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1;P5.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ETOH_B2_012</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1', 'final_main_pathways': 'P1', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'isotope;product inference', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P1.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ETOH_B2_015</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P5', 'final_main_pathways': nan, 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;product inference', 'ai_paper_reason': 'Sentence-level AI review found pathway mentions for P5, but no main-pathway claim.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ETOH_B2_017</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>low_confidence_but_included</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1 included rows</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P3', 'final_main_pathways': 'P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT;operando/spectroscopy;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown', 'ai_paper_reason': 'Sentence-level AI review found main-pathway evidence for P2.', 'ai_paper_confidence': 'low', 'final_include': 'yes'}</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>P1;P2;P3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>P1 is supported by direct spectroscopic detection of *OCCOH and *OCH2CH3 intermediates for ethanol. P2 lacks complete pathway evidence, and P3 is the upstream coupling step; both are mentioned as alternative or supporting routes.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>use_resolved_result</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/05_statistics/pathway_conflict_ai_resolved.xlsx
+++ b/05_statistics/pathway_conflict_ai_resolved.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P2;P5', 'final_main_pathways': 'P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper proposes a tandem catalyst with dual active sites (Sn and O) that enable C-C coupling between *CHO and *CO(OH) (P2) and between formate/HCOOH and *CO(OH) (P5) to form ethanol. Evidence includes DFT calculations, isotope labeling, and product distribution experiments.', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P2;P5', 'final_main_pathways': 'P2;P5', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要报道了Sn基串联催化剂将CO2还原为乙醇，提出了两种主要路径：P2 (*CHO和*CO(OH)偶联)和P5 (甲酸/碳酸氢盐中间体与CO偶联)。通过DFT计算、同位素标记实验和产物分布分析证实了这些路径，所有证据均明确指向乙醇生成。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P2;P5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Isotope labeling experiments (S0050) directly support P5 (formate/HCOOH coupling with *CO(OH)), while P2 (*CHO + *CO(OH)) is discussed but lacks direct experimental confirmation. DFT evidence for P5 is also strong, and the paper's main conclusion emphasizes the formate-bicarbonate coupling pathway.</t>
+          <t>The paper explicitly proposes a tandem mechanism where P5 (formate/bicarbonate coupling with CO) generates *CO(OH) and P2 (*CHO and *CO(OH) coupling) forms the C-C bond, supported by DFT and isotope experiments. Both pathways are integral and clearly presented as main mechanisms.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P3;P6', 'final_main_pathways': 'P1;P3;P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1; P3; P6', 'final_main_pathways': 'P1; P3; P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'Main pathways P1, P3, P6 are supported by operando spectroscopy (Raman/SERS) identifying *OCCO(H), *CHCO reduction to *OCHCH2, and *OCHCH intermediates. However, P6 is also rejected by DFT simulations on distorted sites, creating a conflict. Ethanol is specifically addressed but some P1 evidence relates to ethylene only.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>P3;P6</t>
+          <t>P1;P3;P6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>P1;P3;P6</t>
+          <t>P1;P2;P3;P5;P6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>P3 and P6 are directly supported by operando spectroscopy evidence for ethanol. P1 is mainly associated with ethylene, and its ethanol specificity is weaker. The conflict for P6 arises because DFT rejects CO-CH coupling (one mechanism), but SERS confirms the *OCHCH intermediate, so the pathway is retained. P1 is demoted to mentioned pathway due to lack of strong ethanol evidence.</t>
+          <t>The paper presents three main pathways for ethanol: P1 via OCCO(H) intermediate (correlated with ethanol through FE correlation), P3 via CHCO reduction to OCHCH2 (explicitly identified as selectivity switch to ethanol), and P6 via OCHCH intermediate on defective sites (supported by operando SERS evidence). The rejection of P6 by DFT is specific to distorted sites and does not negate its role on defective surfaces; thus all three are context-dependent main pathways. P2 and P5 are only mentioned as alternatives or for other products and are not main for ethanol.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P3;P6', 'final_main_pathways': 'P1;P3;P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1; P3; P6', 'final_main_pathways': 'P1; P3; P6', 'final_rejected_pathways': 'P6', 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'Main pathways P1, P3, P6 are supported by operando spectroscopy (Raman/SERS) identifying *OCCO(H), *CHCO reduction to *OCHCH2, and *OCHCH intermediates. However, P6 is also rejected by DFT simulations on distorted sites, creating a conflict. Ethanol is specifically addressed but some P1 evidence relates to ethylene only.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -582,12 +582,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>P1;P3;P5;P6</t>
+          <t>P1;P3;P6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>P1 (OCCO pathway) is supported by operando spectroscopy for ethylene and ethanol; P3 (*CHCO→*OCHCH2) is directly identified as selectivity switch to ethanol; P6 (*OCHCH) is confirmed as common intermediate by SERS and labeling experiments, despite DFT rejecting CO-CH coupling on defective sites (which is a separate mechanism). The rejection of P6 in sentence S0044 refers specifically to CO-CH coupling, not the *OCHCH pathway supported elsewhere. Therefore, P6 is retained as main pathway.</t>
+          <t>P6 is supported by experimental evidence (SERS identification of *OCHCH) as an ethanol pathway; the DFT rejection in S0044 applies only to distorted sites and does not negate the pathway overall. Thus P6 should remain as a main pathway.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P3;P4', 'final_main_pathways': 'P1;P3;P4', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'This paper focuses on electrocatalytic CO2 reduction to ethanol via subsurface Co-doped CuS catalyst. The main pathways involve asymmetric C-C coupling (*CO + *COH → *OCCOH) and subsequent hydrogenation steps to ethanol (P1, P3, P4), supported by DFT calculations and in-situ FTIR spectroscopy. Key evidence includes explicit ethanol pathway in S0246 and shared intermediate *CHCHO in S0040.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P3;P4', 'final_main_pathways': 'P1;P3;P4', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'DFT', 'ai_paper_reason': '主要基于DFT计算和in-situ FTIR验证，提出了从CO2到乙醇的完整路径，包括*OCCOH不对称偶联和*CHCHO中间体转化。主路径为P1,P3,P4。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -629,12 +629,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The paper presents a complete ethanol pathway from CO to ethanol via asymmetric C-C coupling (*CO+*COH→*OCCOH) and subsequent hydrogenation steps including *CHCHO intermediate. Sentence S0246 explicitly lists this pathway, which corresponds to P1, P3, and P4 as a sequential mechanism. Therefore, all three pathways are supported as main pathways in a unified mechanism, consistent with the original paper summary.</t>
+          <t>The paper explicitly proposes a complete reaction pathway from CO2 to ethanol in sentence S0246, which includes the key steps *OCCOH (P1), *CHCHO (P3), and further conversion to ethanol, consistent with the paper-level summary. Additional evidence from S0160 (P1) and S0040 (P4) supports these pathways. The multiple main pathways represent a sequential mechanism, not competing alternatives, and are all directly supported by DFT and in-situ FTIR evidence.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>keep_paper_summary</t>
+          <t>use_resolved_result</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P2', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '通过DFT和原位光谱证实CA分子促进*OC2H3中间体C-O键保留，有利于乙醇生成，主要路径为P1和P2。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P2', 'final_main_pathways': 'P1;P2', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'yes', 'main_evidence_basis': 'mixed', 'ai_paper_reason': '论文通过DFT和原位拉曼光谱确认了*OCCOH和*OC2H5中间体，并在CA存在下促进乙醇生成，因此主要路径为P1和P2。', 'ai_paper_confidence': 'high', 'final_include': 'yes'}</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>The paper explicitly identifies P1 and P2 as the main pathways, supported by DFT and operando spectroscopy evidence. Low-confidence sentences that do not mention ethanol pathways are excluded. The conflict is resolved by retaining both pathways as main, consistent with the original paper-level summary.</t>
+          <t>Both P1 and P2 are supported by explicit DFT and in-situ Raman evidence as key intermediates (OCCOH and OC2H5) in the ethanol formation pathway, indicating a cooperative or sequential mechanism, so both should be retained as main pathways.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'final_mentioned_pathways': 'P1;P2;P3', 'final_main_pathways': 'P1;P2;P3', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper focuses on low-coordinated Cu catalysts for CO2 reduction to C2+ alcohols, primarily ethanol. DFT calculations and operando Raman spectroscopy identify pathways P1 (*OCCOH intermediate via *CO-COH coupling), P2 (*CH2CO intermediate), and P3 (*CO-COH coupling) as main routes. Evidence includes DFT energy barriers and spectroscopic detection of key intermediates (*OCCOH, *CHO, *OCH2CH3). While ethanol is the dominant product (FE ~56%), the paper often refers to C2+ alcohols generally, leading to a partial ethanol-specific level.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
+          <t>{'final_mentioned_pathways': 'P1;P2;P3', 'final_main_pathways': 'P1;P2;P3', 'final_rejected_pathways': nan, 'ethanol_specific_level': 'partial', 'main_evidence_basis': 'mixed', 'ai_paper_reason': 'The paper presents DFT calculations and operando Raman spectroscopy to elucidate pathways for CO2 reduction to C2+ alcohols on Cu/Cu2O catalysts. Key evidence supports *CO-COH coupling (P3) and *OCCOH intermediate (P1) for ethanol formation, with minor mention of *CH2CO affinity (P2). Although ethanol is a major product (FE ~56%), some evidence is generalized to C2+ alcohols, leading to partial ethanol specificity.', 'ai_paper_confidence': 'medium', 'final_include': 'yes'}</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1;P3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>P1 is supported by direct spectroscopic detection of *OCCOH and *OCH2CH3 intermediates for ethanol. P2 lacks complete pathway evidence, and P3 is the upstream coupling step; both are mentioned as alternative or supporting routes.</t>
+          <t>P1 and P3 are both supported by strong DFT and operando Raman evidence for ethanol formation: P1 (*OCCOH intermediate) is detected directly, and P3 (*CO-COH coupling) is the rate-determining step. They are parts of the same overall pathway. P2 is only mentioned in one sentence with weak evidence, so it should be mentioned but not main.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
